--- a/lab-standards/ISC-T&H-lab-standard.xlsx
+++ b/lab-standards/ISC-T&H-lab-standard.xlsx
@@ -559,6 +559,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -572,6 +576,10 @@
 Workshop/ lab – 800 sft (75 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -641,7 +649,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -663,7 +673,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -685,7 +697,9 @@
       <c r="C18" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -707,7 +721,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -729,7 +745,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -751,7 +769,9 @@
       <c r="C21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -773,7 +793,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -795,7 +817,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -817,7 +841,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -839,7 +865,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -861,7 +889,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -883,7 +913,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -905,7 +937,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -927,7 +961,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -949,7 +985,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>5</v>
       </c>
@@ -971,7 +1009,9 @@
       <c r="C31" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -993,7 +1033,9 @@
       <c r="C32" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
@@ -1015,7 +1057,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>4</v>
       </c>
@@ -1037,7 +1081,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>3</v>
       </c>
@@ -1183,6 +1229,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1197,6 +1247,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1266,7 +1320,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1288,7 +1344,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1310,7 +1368,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -1332,7 +1392,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -1354,7 +1416,9 @@
       <c r="C20" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -1376,7 +1440,9 @@
       <c r="C21" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -1398,7 +1464,9 @@
       <c r="C22" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -1424,7 +1492,9 @@
       <c r="C23" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -1450,7 +1520,9 @@
       <c r="C24" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -1476,7 +1548,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -1498,7 +1572,9 @@
       <c r="C26" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -1520,7 +1596,9 @@
       <c r="C27" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -1542,7 +1620,9 @@
       <c r="C28" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
@@ -1564,7 +1644,9 @@
       <c r="C29" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -1586,7 +1668,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -1608,7 +1692,9 @@
       <c r="C31" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -1630,7 +1716,9 @@
       <c r="C32" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>3</v>
       </c>
@@ -1652,7 +1740,9 @@
       <c r="C33" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -1674,7 +1764,9 @@
       <c r="C34" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -1696,7 +1788,9 @@
       <c r="C35" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -1718,7 +1812,9 @@
       <c r="C36" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -1740,7 +1836,9 @@
       <c r="C37" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>4</v>
       </c>
@@ -1762,7 +1860,9 @@
       <c r="C38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>6</v>
       </c>
@@ -1784,7 +1884,9 @@
       <c r="C39" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>4</v>
       </c>
@@ -1806,7 +1908,9 @@
       <c r="C40" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>4</v>
       </c>
@@ -1828,7 +1932,9 @@
       <c r="C41" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>3</v>
       </c>
@@ -1854,7 +1960,9 @@
       <c r="C42" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>3</v>
       </c>
@@ -1876,7 +1984,9 @@
       <c r="C43" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="9" t="n">
         <v>3</v>
       </c>
@@ -1898,7 +2008,9 @@
       <c r="C44" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D44" s="9" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="9" t="n">
         <v>3</v>
       </c>
@@ -1920,7 +2032,9 @@
       <c r="C45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="9" t="n"/>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="9" t="n">
         <v>3</v>
       </c>
@@ -1942,7 +2056,9 @@
       <c r="C46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="9" t="n"/>
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="9" t="n">
         <v>3</v>
       </c>
@@ -2088,6 +2204,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2101,6 +2221,10 @@
 Workshop/ lab – 800 sft. (75 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2170,7 +2294,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2192,7 +2318,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2214,7 +2342,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -2248,7 +2378,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -2274,7 +2406,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>3</v>
       </c>
@@ -2296,7 +2430,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -2318,7 +2454,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -2344,7 +2482,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -2366,7 +2506,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -2388,7 +2530,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -2410,7 +2554,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -2432,7 +2578,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -2454,7 +2602,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -2476,7 +2626,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -2498,7 +2650,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>5</v>
       </c>
@@ -2524,7 +2678,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>5</v>
       </c>
@@ -2550,7 +2706,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -2572,7 +2730,9 @@
       <c r="C33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -2594,7 +2754,9 @@
       <c r="C34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>3</v>
       </c>
@@ -2616,7 +2778,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -2638,7 +2802,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>5</v>
       </c>
@@ -2660,7 +2826,9 @@
       <c r="C37" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>8</v>
       </c>
@@ -2682,7 +2850,9 @@
       <c r="C38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>3</v>
       </c>
@@ -2704,7 +2874,9 @@
       <c r="C39" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>3</v>
       </c>
@@ -2726,7 +2898,9 @@
       <c r="C40" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>4</v>
       </c>
@@ -2748,7 +2922,9 @@
       <c r="C41" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>4</v>
       </c>
@@ -2770,7 +2946,9 @@
       <c r="C42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>3</v>
       </c>
@@ -2916,6 +3094,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2929,6 +3111,10 @@
 Workshop/ lab – 800 sft (75 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2998,7 +3184,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3020,7 +3208,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3042,7 +3232,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -3064,7 +3256,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -3086,7 +3280,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -3108,7 +3304,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -3130,7 +3328,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -3152,7 +3352,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -3174,7 +3376,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -3196,7 +3400,9 @@
       <c r="C25" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -3218,7 +3424,9 @@
       <c r="C26" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>3</v>
       </c>
@@ -3240,7 +3448,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -3262,7 +3472,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -3284,7 +3496,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>8</v>
       </c>
@@ -3306,7 +3520,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -3328,7 +3544,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -3350,7 +3568,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -3372,7 +3592,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -3394,7 +3616,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
@@ -3416,7 +3640,9 @@
       <c r="C35" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -3438,7 +3664,9 @@
       <c r="C36" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -3460,7 +3688,9 @@
       <c r="C37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>4</v>
       </c>
@@ -3482,7 +3712,9 @@
       <c r="C38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>3</v>
       </c>

--- a/lab-standards/ISC-T&H-lab-standard.xlsx
+++ b/lab-standards/ISC-T&H-lab-standard.xlsx
@@ -725,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>

--- a/lab-standards/ISC-T&H-lab-standard.xlsx
+++ b/lab-standards/ISC-T&H-lab-standard.xlsx
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Weighing Scale (Preferred capacity 1 kg)</t>
+          <t>Weighing Scale (Preferred capacity 5 kg)</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">

--- a/lab-standards/ISC-T&H-lab-standard.xlsx
+++ b/lab-standards/ISC-T&H-lab-standard.xlsx
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -1496,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -1768,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35" s="9">
         <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" s="9">
         <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F37" s="9">
         <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
@@ -1864,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F38" s="9">
         <f>IFERROR(MIN(C38,D38)*E38/C38,0)</f>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39" s="9">
         <f>IFERROR(MIN(C39,D39)*E39/C39,0)</f>
@@ -1912,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40" s="9">
         <f>IFERROR(MIN(C40,D40)*E40/C40,0)</f>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -2510,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -2582,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
@@ -2682,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F31" s="9">
         <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" s="9">
         <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
@@ -2830,7 +2830,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F37" s="9">
         <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="9">
         <f>IFERROR(MIN(C38,D38)*E38/C38,0)</f>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="9">
         <f>IFERROR(MIN(C39,D39)*E39/C39,0)</f>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F41" s="9">
         <f>IFERROR(MIN(C41,D41)*E41/C41,0)</f>
@@ -3404,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -3596,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33" s="9">
         <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
